--- a/data/credit_bond_all_2026-10-30.xlsx
+++ b/data/credit_bond_all_2026-10-30.xlsx
@@ -700,7 +700,11 @@
           <t>11-02 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>102684371.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -739,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/1.6200</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -779,7 +783,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -920,7 +928,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>102684366.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>2+N</t>
@@ -959,7 +971,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8400</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -999,7 +1011,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2.06%~2.16%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1123,7 +1139,9 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1136,7 +1154,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>102684367.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -1175,7 +1197,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.1000</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1215,7 +1237,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X5" s="3"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>2.22%~2.32%</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1339,7 +1365,9 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="AZ5" s="3"/>
+      <c r="AZ5" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
@@ -1395,7 +1423,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5900</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1435,7 +1463,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>1.54%~1.64%</t>
+        </is>
+      </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1576,7 +1608,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>012682574.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -1655,7 +1691,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X7" s="3"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>1.44%~1.48%</t>
+        </is>
+      </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1792,7 +1832,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>102684362.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1831,7 +1875,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6810</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1871,7 +1915,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X8" s="3"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2012,7 +2060,11 @@
           <t>11-02 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>102684370.IB</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2051,7 +2103,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6800</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2091,7 +2143,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X9" s="3"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2215,7 +2271,9 @@
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -2311,7 +2369,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>2.13%~2.23%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2535,7 +2597,11 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>3.09%~3.19%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2668,7 +2734,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>102684328.IB</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -2677,7 +2747,9 @@
       <c r="E12" s="4" t="n">
         <v>7.0</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>1.10 ~ 2.10</t>
@@ -2747,7 +2819,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X12" s="3"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>1.56%~1.66%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2884,7 +2960,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>102684364.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>2+N</t>
@@ -2963,7 +3043,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X13" s="3"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3087,7 +3171,9 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="AZ13" s="3"/>
+      <c r="AZ13" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
@@ -3143,7 +3229,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3183,7 +3269,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.79%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3403,7 +3493,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.67%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3579,7 +3673,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7200</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3619,7 +3713,11 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>2.98%~3.08%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -3747,7 +3845,9 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
@@ -3799,7 +3899,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7900</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -3839,7 +3939,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.92%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3963,7 +4067,9 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
@@ -4281,7 +4387,11 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>2.25%~2.35%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -4445,14 +4555,22 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>26潮升K1</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>4.66Y</t>
+        </is>
+      </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.8359</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4626,7 +4744,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>012682572.IB</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -4665,7 +4787,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4300</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -4705,7 +4827,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X21" s="3"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>1.43%~1.47%</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4842,7 +4968,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>012682573.IB</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -4921,7 +5051,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X22" s="3"/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1.45%~1.49%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5054,7 +5188,11 @@
           <t>11-02 18:00</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>102684369.IB</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -5093,7 +5231,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6800</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -5133,7 +5271,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X23" s="3"/>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5261,7 +5403,9 @@
           <t>2026-11-02</t>
         </is>
       </c>
-      <c r="AZ23" s="3"/>
+      <c r="AZ23" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
@@ -5357,7 +5501,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X24" s="3"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>1.89%~1.99%</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -5498,7 +5646,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C25" s="3"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>102684365.IB</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -5577,7 +5729,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X25" s="3"/>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1.55%~1.65%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5714,7 +5870,11 @@
           <t>10-30 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>102684368.IB</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -5793,7 +5953,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X26" s="3"/>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>2.14%~2.24%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5917,7 +6081,9 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
